--- a/data/raw/01_FormatosRA_ReformaCurricular/FormatoRA_ECENJA_PBOG.xlsx
+++ b/data/raw/01_FormatosRA_ReformaCurricular/FormatoRA_ECENJA_PBOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/01_FormatosRA_ReformaCurricular/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/01_FormatosRA_ReformaCurricular/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="420" documentId="8_{4A0F5AF3-8D72-6746-8BDD-E47DE49BEC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A52EB88-8661-4ABB-BDBF-BEF874ABB9E8}"/>
+  <xr:revisionPtr revIDLastSave="425" documentId="8_{4A0F5AF3-8D72-6746-8BDD-E47DE49BEC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E202F7-24CA-4D71-BACB-46E7BE60BA1F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{BD68381A-4EB3-42BA-ADD5-D7B5B6C7E498}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
@@ -2751,9 +2751,6 @@
     <t>Tipología</t>
   </si>
   <si>
-    <t>Fudamentación</t>
-  </si>
-  <si>
     <t>Número de horas trabajo directo</t>
   </si>
   <si>
@@ -2920,6 +2917,9 @@
   </si>
   <si>
     <t>Especialista o asesor jurídico en contratación estatal e institucional/Coordinador de gestión contractual/Consultor en procesos de contratación pública/Especialista en planeación y evaluación contractual/Auditor, interventor o supervisor jurídico de contratos/Coordinador de control y cumplimiento contractual/Consultor en estructuración de negocios jurídicos públicos/Coordinador de convenios y proyectos interinstitucionales/Especialista en gestión de asociaciones y contratos interadministrativos/Asesor jurídico externo en contratación y responsabilidad contractual pública/Especialista en análisis normativo y regulación contractual/Investigador o consultor en políticas de contratación estatal/Formador o capacitador en gestión y normatividad contractual/Redactor o desarrollador de manuales y guías de buenas prácticas contractuales/Especialista en gestión documental y transparencia contractual/Lider en procesos de información y trazabilidad contractual (SECOP)/Asesor en políticas de transparencia y rendición de cuentas.</t>
+  </si>
+  <si>
+    <t>Fundamentación</t>
   </si>
 </sst>
 </file>
@@ -3720,66 +3720,6 @@
     <xf numFmtId="0" fontId="23" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3793,6 +3733,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3843,6 +3786,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3863,6 +3821,48 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9230,23 +9230,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46FA7EDF-246F-4EE0-BFE4-7EACACD45C48}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.36328125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.33203125" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.08984375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="62.6328125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="97.26953125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="41.453125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="43.81640625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="50.54296875" style="4" customWidth="1"/>
-    <col min="8" max="8" width="76.81640625" style="4" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="62.6640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="97.21875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="43.77734375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="50.5546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="76.77734375" style="4" customWidth="1"/>
     <col min="9" max="9" width="64" style="4" customWidth="1"/>
-    <col min="10" max="10" width="63.90625" style="4" customWidth="1"/>
-    <col min="11" max="11" width="75.6328125" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="76.36328125" style="4"/>
+    <col min="10" max="10" width="63.88671875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="75.6640625" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="76.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>536</v>
       </c>
@@ -9259,21 +9259,21 @@
       <c r="D1" s="47" t="s">
         <v>539</v>
       </c>
-      <c r="E1" s="83" t="s">
+      <c r="E1" s="114" t="s">
         <v>542</v>
       </c>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83" t="s">
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114" t="s">
         <v>543</v>
       </c>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
       <c r="K1" s="49" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" s="5" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48" t="s">
         <v>0</v>
       </c>
@@ -9308,65 +9308,65 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="81.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="82" t="s">
+    <row r="3" spans="1:11" ht="81.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="84" t="s">
         <v>532</v>
       </c>
-      <c r="B3" s="82" t="s">
+      <c r="B3" s="84" t="s">
         <v>533</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="101" t="s">
         <v>535</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="101" t="s">
         <v>534</v>
       </c>
       <c r="E3" s="38" t="s">
+        <v>624</v>
+      </c>
+      <c r="F3" s="38" t="s">
         <v>625</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="G3" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="H3" s="113" t="s">
+        <v>649</v>
+      </c>
+      <c r="I3" s="113" t="s">
+        <v>639</v>
+      </c>
+      <c r="J3" s="113" t="s">
+        <v>631</v>
+      </c>
+      <c r="K3" s="113" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="81.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="38" t="s">
         <v>626</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="H3" s="79" t="s">
-        <v>650</v>
-      </c>
-      <c r="I3" s="79" t="s">
-        <v>640</v>
-      </c>
-      <c r="J3" s="79" t="s">
-        <v>632</v>
-      </c>
-      <c r="K3" s="79" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="81.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="82"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="38" t="s">
-        <v>627</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="H4" s="80"/>
-      <c r="I4" s="80"/>
-      <c r="J4" s="80"/>
-      <c r="K4" s="80"/>
-    </row>
-    <row r="5" spans="1:11" ht="81.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="82"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
+        <v>628</v>
+      </c>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
+      <c r="K4" s="103"/>
+    </row>
+    <row r="5" spans="1:11" ht="81.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
       <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
@@ -9374,34 +9374,34 @@
         <v>11</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>629</v>
+      </c>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
@@ -9432,30 +9432,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81C1850E-A9C8-4F69-8E80-DEAF9721FFBF}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="4" customWidth="1"/>
-    <col min="2" max="2" width="24.26953125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="41.453125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="48.81640625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="52.08984375" style="4" customWidth="1"/>
-    <col min="6" max="6" width="105.36328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="34.54296875" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="4"/>
+    <col min="2" max="2" width="24.21875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="41.44140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="48.77734375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="52.109375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="105.33203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="34.5546875" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="52" x14ac:dyDescent="0.5">
+      <c r="B1" s="116"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="116"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="116"/>
+    </row>
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="48" x14ac:dyDescent="0.5">
       <c r="A2" s="50" t="s">
         <v>545</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="53" t="s">
         <v>552</v>
       </c>
@@ -9501,7 +9501,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -9509,22 +9509,22 @@
         <v>13</v>
       </c>
       <c r="C4" s="60" t="s">
+        <v>624</v>
+      </c>
+      <c r="D4" s="60" t="s">
         <v>625</v>
       </c>
-      <c r="D4" s="60" t="s">
-        <v>626</v>
-      </c>
       <c r="E4" s="60" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="49.5" x14ac:dyDescent="0.35">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -9532,22 +9532,22 @@
         <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="49.5" x14ac:dyDescent="0.35">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -9561,20 +9561,20 @@
         <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="29"/>
       <c r="D7" s="5"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="29"/>
     </row>
   </sheetData>
@@ -9618,22 +9618,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AAF649-42F4-466A-BE11-44357078F961}">
   <dimension ref="A1:J124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="93.36328125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16.6328125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="19.1796875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="34.08984375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="17.81640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="20.1796875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="18.36328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="82.6328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="43.36328125" style="5" customWidth="1"/>
-    <col min="11" max="16384" width="11.453125" style="5"/>
+    <col min="1" max="1" width="93.33203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="34.109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="82.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="43.33203125" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="78" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="84" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>559</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="33.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="74" t="s">
         <v>568</v>
       </c>
@@ -9691,9 +9691,9 @@
         <v>576</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="75" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B3" s="23">
         <v>1</v>
@@ -9702,7 +9702,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>17</v>
@@ -9721,9 +9721,9 @@
       </c>
       <c r="J3" s="28"/>
     </row>
-    <row r="4" spans="1:10" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="90" x14ac:dyDescent="0.3">
       <c r="A4" s="76" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B4" s="6">
         <v>2</v>
@@ -9732,7 +9732,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>17</v>
@@ -9751,9 +9751,9 @@
       </c>
       <c r="J4" s="28"/>
     </row>
-    <row r="5" spans="1:10" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="76" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B5" s="6">
         <v>3</v>
@@ -9762,7 +9762,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>17</v>
@@ -9781,9 +9781,9 @@
       </c>
       <c r="J5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="54" x14ac:dyDescent="0.3">
       <c r="A6" s="75" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B6" s="23">
         <v>4</v>
@@ -9792,7 +9792,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>17</v>
@@ -9811,9 +9811,9 @@
       </c>
       <c r="J6" s="28"/>
     </row>
-    <row r="7" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="76" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B7" s="6">
         <v>5</v>
@@ -9840,9 +9840,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="76" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
@@ -9851,7 +9851,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>17</v>
@@ -9866,10 +9866,10 @@
         <v>33</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="54" x14ac:dyDescent="0.3">
       <c r="A9" s="75" t="s">
         <v>16</v>
       </c>
@@ -9898,7 +9898,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="76" t="s">
         <v>16</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="66.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="77" t="s">
         <v>16</v>
       </c>
@@ -9938,7 +9938,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>17</v>
@@ -9956,7 +9956,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -10464,18 +10464,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F726B80-E6B4-4ED4-A764-E59AF4E18393}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="82.1796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="58.453125" style="35" customWidth="1"/>
-    <col min="4" max="4" width="61.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="39.1796875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="43.1796875" style="29" customWidth="1"/>
-    <col min="7" max="16384" width="11.453125" style="1"/>
+    <col min="1" max="1" width="82.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="48.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="58.44140625" style="35" customWidth="1"/>
+    <col min="4" max="4" width="61.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="29" customWidth="1"/>
+    <col min="7" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="29" customFormat="1" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="29" customFormat="1" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>577</v>
       </c>
@@ -10495,7 +10495,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="29" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" s="29" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
         <v>583</v>
       </c>
@@ -10515,137 +10515,137 @@
         <v>588</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="33" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A3" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="98" t="s">
+      <c r="C3" s="105" t="s">
         <v>41</v>
       </c>
       <c r="D3" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="86" t="s">
-        <v>637</v>
+      <c r="E3" s="117" t="s">
+        <v>636</v>
       </c>
       <c r="F3" s="40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="49.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" ht="54" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="80"/>
+      <c r="B4" s="121"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="87"/>
+      <c r="E4" s="118"/>
       <c r="F4" s="29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="93"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="104"/>
       <c r="D5" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="88"/>
+      <c r="E5" s="119"/>
       <c r="F5" s="33" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="33" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A6" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="92" t="s">
-        <v>639</v>
+      <c r="C6" s="102" t="s">
+        <v>638</v>
       </c>
       <c r="D6" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="94" t="s">
-        <v>638</v>
+      <c r="E6" s="123" t="s">
+        <v>637</v>
       </c>
       <c r="F6" s="31" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="82.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="80"/>
+      <c r="B7" s="121"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="95"/>
+      <c r="E7" s="124"/>
       <c r="F7" s="29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="33" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:6" ht="36" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="90"/>
-      <c r="C8" s="80"/>
+      <c r="B8" s="121"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="95"/>
+      <c r="E8" s="124"/>
       <c r="F8" s="29" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="49.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:6" ht="54" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="90"/>
-      <c r="C9" s="80"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="45"/>
-      <c r="E9" s="95"/>
-    </row>
-    <row r="10" spans="1:6" ht="66" x14ac:dyDescent="0.5">
+      <c r="E9" s="124"/>
+    </row>
+    <row r="10" spans="1:6" ht="72" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="90"/>
-      <c r="C10" s="80"/>
+      <c r="B10" s="121"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="45"/>
-      <c r="E10" s="95"/>
-    </row>
-    <row r="11" spans="1:6" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="E10" s="124"/>
+    </row>
+    <row r="11" spans="1:6" ht="54" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="B11" s="90"/>
-      <c r="C11" s="80"/>
+        <v>635</v>
+      </c>
+      <c r="B11" s="121"/>
+      <c r="C11" s="103"/>
       <c r="D11" s="45"/>
-      <c r="E11" s="95"/>
-    </row>
-    <row r="12" spans="1:6" ht="50" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E11" s="124"/>
+    </row>
+    <row r="12" spans="1:6" ht="54.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="91"/>
-      <c r="C12" s="93"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="46"/>
-      <c r="E12" s="96"/>
+      <c r="E12" s="125"/>
       <c r="F12" s="33"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.5">
@@ -10686,27 +10686,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B248250-C92C-4D02-A0C3-2CB27C341894}">
   <dimension ref="A1:P45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.453125" style="1"/>
-    <col min="2" max="2" width="65.7265625" style="29" customWidth="1"/>
-    <col min="3" max="3" width="17.36328125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="41.6328125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="72.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.453125" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.7265625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" style="7" customWidth="1"/>
-    <col min="10" max="10" width="20.54296875" style="7" customWidth="1"/>
-    <col min="11" max="11" width="24.453125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="17.6328125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" style="1"/>
+    <col min="2" max="2" width="65.77734375" style="29" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="72.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.77734375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="20.5546875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="7" customWidth="1"/>
     <col min="13" max="13" width="53" style="22" customWidth="1"/>
-    <col min="14" max="14" width="70.6328125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="77.1796875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="73.1796875" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="11.453125" style="1"/>
+    <col min="14" max="14" width="70.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="77.21875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="73.21875" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="6" customFormat="1" ht="65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="6" customFormat="1" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>589</v>
       </c>
@@ -10725,10 +10725,10 @@
       <c r="F1" s="47" t="s">
         <v>594</v>
       </c>
-      <c r="G1" s="123" t="s">
+      <c r="G1" s="109" t="s">
         <v>595</v>
       </c>
-      <c r="H1" s="124"/>
+      <c r="H1" s="110"/>
       <c r="I1" s="47" t="s">
         <v>596</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="6" customFormat="1" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" s="6" customFormat="1" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
         <v>51</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>607</v>
       </c>
       <c r="G2" s="63" t="s">
-        <v>608</v>
+        <v>650</v>
       </c>
       <c r="H2" s="63" t="s">
         <v>54</v>
@@ -10783,28 +10783,28 @@
         <v>52</v>
       </c>
       <c r="J2" s="57" t="s">
+        <v>608</v>
+      </c>
+      <c r="K2" s="57" t="s">
         <v>609</v>
-      </c>
-      <c r="K2" s="57" t="s">
-        <v>610</v>
       </c>
       <c r="L2" s="57" t="s">
         <v>53</v>
       </c>
       <c r="M2" s="57" t="s">
+        <v>610</v>
+      </c>
+      <c r="N2" s="57" t="s">
         <v>611</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="O2" s="57" t="s">
         <v>612</v>
       </c>
-      <c r="O2" s="57" t="s">
+      <c r="P2" s="57" t="s">
         <v>613</v>
       </c>
-      <c r="P2" s="57" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="58" customHeight="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="3" spans="1:16" ht="58.05" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A3" s="29" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10812,51 +10812,51 @@
       <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="118">
+      <c r="C3" s="99">
         <v>1</v>
       </c>
-      <c r="D3" s="103" t="s">
+      <c r="D3" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="121" t="s">
-        <v>649</v>
-      </c>
-      <c r="F3" s="118" t="s">
+      <c r="E3" s="107" t="s">
+        <v>648</v>
+      </c>
+      <c r="F3" s="99" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="82" t="s">
+      <c r="G3" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="82"/>
-      <c r="I3" s="103">
+      <c r="H3" s="84"/>
+      <c r="I3" s="83">
         <v>3</v>
       </c>
-      <c r="J3" s="82">
+      <c r="J3" s="84">
         <f>12*I3</f>
         <v>36</v>
       </c>
-      <c r="K3" s="82">
+      <c r="K3" s="84">
         <f>36*I3</f>
         <v>108</v>
       </c>
-      <c r="L3" s="82">
+      <c r="L3" s="84">
         <f>SUM(J3:K5)</f>
         <v>144</v>
       </c>
-      <c r="M3" s="122" t="s">
-        <v>616</v>
-      </c>
-      <c r="N3" s="125" t="s">
+      <c r="M3" s="108" t="s">
+        <v>615</v>
+      </c>
+      <c r="N3" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="O3" s="98" t="s">
+      <c r="O3" s="105" t="s">
         <v>59</v>
       </c>
-      <c r="P3" s="99" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="P3" s="79" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A4" s="29" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -10864,22 +10864,22 @@
       <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="80"/>
-      <c r="P4" s="100"/>
-    </row>
-    <row r="5" spans="1:16" ht="99.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C4" s="92"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="92"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="101"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="80"/>
+    </row>
+    <row r="5" spans="1:16" ht="108.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="33" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -10887,22 +10887,22 @@
       <c r="B5" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="112"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="104"/>
-      <c r="L5" s="104"/>
-      <c r="M5" s="120"/>
-      <c r="N5" s="120"/>
-      <c r="O5" s="93"/>
-      <c r="P5" s="101"/>
-    </row>
-    <row r="6" spans="1:16" ht="33" x14ac:dyDescent="0.5">
+      <c r="C5" s="93"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="85"/>
+      <c r="H5" s="85"/>
+      <c r="I5" s="85"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="81"/>
+    </row>
+    <row r="6" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A6" s="31" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10910,51 +10910,51 @@
       <c r="B6" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="110">
+      <c r="C6" s="91">
         <v>1</v>
       </c>
-      <c r="D6" s="113" t="s">
+      <c r="D6" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="116" t="s">
-        <v>648</v>
-      </c>
-      <c r="F6" s="110" t="s">
+      <c r="E6" s="97" t="s">
+        <v>647</v>
+      </c>
+      <c r="F6" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="113" t="s">
+      <c r="G6" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="113"/>
-      <c r="I6" s="113">
+      <c r="H6" s="94"/>
+      <c r="I6" s="94">
         <v>3</v>
       </c>
-      <c r="J6" s="113">
+      <c r="J6" s="94">
         <f>12*I6</f>
         <v>36</v>
       </c>
-      <c r="K6" s="113">
+      <c r="K6" s="94">
         <f>36*I6</f>
         <v>108</v>
       </c>
-      <c r="L6" s="113">
+      <c r="L6" s="94">
         <f>SUM(J6:K8)</f>
         <v>144</v>
       </c>
-      <c r="M6" s="102" t="s">
-        <v>617</v>
-      </c>
-      <c r="N6" s="102" t="s">
+      <c r="M6" s="82" t="s">
+        <v>616</v>
+      </c>
+      <c r="N6" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O6" s="92" t="s">
+      <c r="O6" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="P6" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="P6" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A7" s="29" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10962,22 +10962,22 @@
       <c r="B7" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="82"/>
-      <c r="H7" s="82"/>
-      <c r="I7" s="82"/>
-      <c r="J7" s="82"/>
-      <c r="K7" s="82"/>
-      <c r="L7" s="82"/>
-      <c r="M7" s="81"/>
-      <c r="N7" s="81"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="100"/>
-    </row>
-    <row r="8" spans="1:16" ht="66.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C7" s="92"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="89"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="101"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="80"/>
+    </row>
+    <row r="8" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="33" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -10985,22 +10985,22 @@
       <c r="B8" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="112"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-      <c r="K8" s="104"/>
-      <c r="L8" s="104"/>
-      <c r="M8" s="120"/>
-      <c r="N8" s="120"/>
-      <c r="O8" s="93"/>
-      <c r="P8" s="101"/>
-    </row>
-    <row r="9" spans="1:16" ht="33" x14ac:dyDescent="0.5">
+      <c r="C8" s="93"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="106"/>
+      <c r="N8" s="106"/>
+      <c r="O8" s="104"/>
+      <c r="P8" s="81"/>
+    </row>
+    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A9" s="31" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11008,51 +11008,51 @@
       <c r="B9" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="110">
+      <c r="C9" s="91">
         <v>1</v>
       </c>
-      <c r="D9" s="113" t="s">
+      <c r="D9" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="116" t="s">
-        <v>647</v>
-      </c>
-      <c r="F9" s="110" t="s">
+      <c r="E9" s="97" t="s">
+        <v>646</v>
+      </c>
+      <c r="F9" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="113" t="s">
+      <c r="G9" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="113">
+      <c r="H9" s="94"/>
+      <c r="I9" s="94">
         <v>3</v>
       </c>
-      <c r="J9" s="113">
+      <c r="J9" s="94">
         <f>12*I9</f>
         <v>36</v>
       </c>
-      <c r="K9" s="113">
+      <c r="K9" s="94">
         <f>36*I9</f>
         <v>108</v>
       </c>
-      <c r="L9" s="113">
+      <c r="L9" s="94">
         <f>SUM(J9:K15)</f>
         <v>144</v>
       </c>
-      <c r="M9" s="102" t="s">
-        <v>618</v>
-      </c>
-      <c r="N9" s="102" t="s">
+      <c r="M9" s="82" t="s">
+        <v>617</v>
+      </c>
+      <c r="N9" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O9" s="102" t="s">
+      <c r="O9" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="P9" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="P9" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A10" s="29" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11060,22 +11060,22 @@
       <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="111"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="111"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="81"/>
-      <c r="N10" s="81"/>
-      <c r="O10" s="81"/>
-      <c r="P10" s="100"/>
-    </row>
-    <row r="11" spans="1:16" ht="99" x14ac:dyDescent="0.5">
+      <c r="C10" s="92"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="89"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
+      <c r="J10" s="84"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="80"/>
+    </row>
+    <row r="11" spans="1:16" ht="108" x14ac:dyDescent="0.5">
       <c r="A11" s="29" t="str">
         <f>_xlfn.XLOOKUP(B11,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11083,22 +11083,22 @@
       <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="111"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="111"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="81"/>
-      <c r="N11" s="81"/>
-      <c r="O11" s="81"/>
-      <c r="P11" s="100"/>
-    </row>
-    <row r="12" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="C11" s="92"/>
+      <c r="D11" s="84"/>
+      <c r="E11" s="89"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="84"/>
+      <c r="H11" s="84"/>
+      <c r="I11" s="84"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="84"/>
+      <c r="L11" s="84"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="80"/>
+    </row>
+    <row r="12" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A12" s="29" t="str">
         <f>_xlfn.XLOOKUP(B12,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11106,22 +11106,22 @@
       <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="111"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="82"/>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="100"/>
-    </row>
-    <row r="13" spans="1:16" ht="66" x14ac:dyDescent="0.5">
+      <c r="C12" s="92"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="101"/>
+      <c r="O12" s="101"/>
+      <c r="P12" s="80"/>
+    </row>
+    <row r="13" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A13" s="29" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11129,22 +11129,22 @@
       <c r="B13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="82"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="82"/>
-      <c r="H13" s="82"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="82"/>
-      <c r="K13" s="82"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="100"/>
-    </row>
-    <row r="14" spans="1:16" ht="66" x14ac:dyDescent="0.5">
+      <c r="C13" s="92"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="89"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="101"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="80"/>
+    </row>
+    <row r="14" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A14" s="29" t="str">
         <f>_xlfn.XLOOKUP(B14,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11152,22 +11152,22 @@
       <c r="B14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82"/>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82"/>
-      <c r="M14" s="81"/>
-      <c r="N14" s="81"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="100"/>
-    </row>
-    <row r="15" spans="1:16" ht="50" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C14" s="92"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="80"/>
+    </row>
+    <row r="15" spans="1:16" ht="54.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="33" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11175,22 +11175,22 @@
       <c r="B15" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="117"/>
-      <c r="F15" s="112"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
-      <c r="P15" s="101"/>
-    </row>
-    <row r="16" spans="1:16" ht="33" x14ac:dyDescent="0.5">
+      <c r="C15" s="93"/>
+      <c r="D15" s="85"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="93"/>
+      <c r="G15" s="85"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="85"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="85"/>
+      <c r="L15" s="85"/>
+      <c r="M15" s="106"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="81"/>
+    </row>
+    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A16" s="31" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11198,51 +11198,51 @@
       <c r="B16" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="110">
+      <c r="C16" s="91">
         <v>1</v>
       </c>
-      <c r="D16" s="113" t="s">
+      <c r="D16" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="116" t="s">
-        <v>646</v>
-      </c>
-      <c r="F16" s="114" t="s">
+      <c r="E16" s="97" t="s">
+        <v>645</v>
+      </c>
+      <c r="F16" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="113" t="s">
+      <c r="G16" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="113"/>
-      <c r="I16" s="113">
+      <c r="H16" s="94"/>
+      <c r="I16" s="94">
         <v>3</v>
       </c>
-      <c r="J16" s="113">
+      <c r="J16" s="94">
         <f>12*I16</f>
         <v>36</v>
       </c>
-      <c r="K16" s="113">
+      <c r="K16" s="94">
         <f>36*I16</f>
         <v>108</v>
       </c>
-      <c r="L16" s="113">
+      <c r="L16" s="94">
         <f>SUM(J16:K20)</f>
         <v>144</v>
       </c>
-      <c r="M16" s="102" t="s">
-        <v>621</v>
-      </c>
-      <c r="N16" s="102" t="s">
+      <c r="M16" s="82" t="s">
+        <v>620</v>
+      </c>
+      <c r="N16" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O16" s="102" t="s">
+      <c r="O16" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="P16" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A17" s="29" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11250,22 +11250,22 @@
       <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="81"/>
-      <c r="P17" s="100"/>
-    </row>
-    <row r="18" spans="1:16" ht="99" x14ac:dyDescent="0.5">
+      <c r="C17" s="92"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="89"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="M17" s="101"/>
+      <c r="N17" s="101"/>
+      <c r="O17" s="101"/>
+      <c r="P17" s="80"/>
+    </row>
+    <row r="18" spans="1:16" ht="108" x14ac:dyDescent="0.5">
       <c r="A18" s="29" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11273,22 +11273,22 @@
       <c r="B18" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="100"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="100"/>
-    </row>
-    <row r="19" spans="1:16" ht="82.5" x14ac:dyDescent="0.5">
+      <c r="C18" s="92"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="89"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="101"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+    </row>
+    <row r="19" spans="1:16" ht="90" x14ac:dyDescent="0.5">
       <c r="A19" s="29" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11296,22 +11296,22 @@
       <c r="B19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="111"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-    </row>
-    <row r="20" spans="1:16" ht="66.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C19" s="92"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+    </row>
+    <row r="20" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="33" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11319,22 +11319,22 @@
       <c r="B20" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="112"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="117"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="120"/>
-      <c r="N20" s="101"/>
-      <c r="O20" s="101"/>
-      <c r="P20" s="101"/>
-    </row>
-    <row r="21" spans="1:16" ht="33" x14ac:dyDescent="0.5">
+      <c r="C20" s="93"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="96"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85"/>
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="106"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="81"/>
+    </row>
+    <row r="21" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A21" s="29" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11342,51 +11342,51 @@
       <c r="B21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="111">
+      <c r="C21" s="92">
         <v>1</v>
       </c>
-      <c r="D21" s="82" t="s">
+      <c r="D21" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="108" t="s">
-        <v>645</v>
-      </c>
-      <c r="F21" s="106" t="s">
+      <c r="E21" s="89" t="s">
+        <v>644</v>
+      </c>
+      <c r="F21" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="82" t="s">
+      <c r="G21" s="84" t="s">
         <v>57</v>
       </c>
-      <c r="H21" s="82"/>
-      <c r="I21" s="82">
+      <c r="H21" s="84"/>
+      <c r="I21" s="84">
         <v>3</v>
       </c>
-      <c r="J21" s="82">
+      <c r="J21" s="84">
         <f>12*I21</f>
         <v>36</v>
       </c>
-      <c r="K21" s="82">
+      <c r="K21" s="84">
         <f>36*I21</f>
         <v>108</v>
       </c>
-      <c r="L21" s="82">
+      <c r="L21" s="84">
         <f>SUM(J21:K24)</f>
         <v>144</v>
       </c>
-      <c r="M21" s="81" t="s">
-        <v>619</v>
-      </c>
-      <c r="N21" s="81" t="s">
+      <c r="M21" s="101" t="s">
+        <v>618</v>
+      </c>
+      <c r="N21" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="O21" s="81" t="s">
+      <c r="O21" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="P21" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="66" x14ac:dyDescent="0.5">
+      <c r="P21" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A22" s="29" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11394,22 +11394,22 @@
       <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="82"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="82"/>
-      <c r="J22" s="82"/>
-      <c r="K22" s="82"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="100"/>
-    </row>
-    <row r="23" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="C22" s="92"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="101"/>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="80"/>
+    </row>
+    <row r="23" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A23" s="29" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11417,22 +11417,22 @@
       <c r="B23" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="82"/>
-      <c r="E23" s="108"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="82"/>
-      <c r="H23" s="82"/>
-      <c r="I23" s="82"/>
-      <c r="J23" s="82"/>
-      <c r="K23" s="82"/>
-      <c r="L23" s="82"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="100"/>
-    </row>
-    <row r="24" spans="1:16" ht="66.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C23" s="92"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="101"/>
+      <c r="N23" s="101"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="80"/>
+    </row>
+    <row r="24" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="33" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11440,22 +11440,22 @@
       <c r="B24" s="37" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="107"/>
-      <c r="G24" s="105"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="105"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="126"/>
-      <c r="N24" s="126"/>
-      <c r="O24" s="126"/>
-      <c r="P24" s="101"/>
-    </row>
-    <row r="25" spans="1:16" ht="33" x14ac:dyDescent="0.5">
+      <c r="C24" s="100"/>
+      <c r="D24" s="86"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="112"/>
+      <c r="N24" s="112"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="81"/>
+    </row>
+    <row r="25" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A25" s="29" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11463,51 +11463,51 @@
       <c r="B25" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="111">
+      <c r="C25" s="92">
         <v>2</v>
       </c>
-      <c r="D25" s="82" t="s">
+      <c r="D25" s="84" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="108" t="s">
-        <v>644</v>
-      </c>
-      <c r="F25" s="106" t="s">
+      <c r="E25" s="89" t="s">
+        <v>643</v>
+      </c>
+      <c r="F25" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111" t="s">
+      <c r="G25" s="92"/>
+      <c r="H25" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="I25" s="111">
+      <c r="I25" s="92">
         <v>2</v>
       </c>
-      <c r="J25" s="82">
+      <c r="J25" s="84">
         <f>12*I25</f>
         <v>24</v>
       </c>
-      <c r="K25" s="82">
+      <c r="K25" s="84">
         <f>36*I25</f>
         <v>72</v>
       </c>
-      <c r="L25" s="82">
+      <c r="L25" s="84">
         <f>SUM(J25:K27)</f>
         <v>96</v>
       </c>
-      <c r="M25" s="81" t="s">
-        <v>622</v>
-      </c>
-      <c r="N25" s="81" t="s">
+      <c r="M25" s="101" t="s">
+        <v>621</v>
+      </c>
+      <c r="N25" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="O25" s="81" t="s">
+      <c r="O25" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="P25" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="99" x14ac:dyDescent="0.5">
+      <c r="P25" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" ht="108" x14ac:dyDescent="0.5">
       <c r="A26" s="29" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11515,22 +11515,22 @@
       <c r="B26" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="82"/>
-      <c r="E26" s="108"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="82"/>
-      <c r="K26" s="82"/>
-      <c r="L26" s="82"/>
-      <c r="M26" s="81"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="81"/>
-      <c r="P26" s="100"/>
-    </row>
-    <row r="27" spans="1:16" ht="50" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C26" s="92"/>
+      <c r="D26" s="84"/>
+      <c r="E26" s="89"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="92"/>
+      <c r="H26" s="92"/>
+      <c r="I26" s="92"/>
+      <c r="J26" s="84"/>
+      <c r="K26" s="84"/>
+      <c r="L26" s="84"/>
+      <c r="M26" s="101"/>
+      <c r="N26" s="101"/>
+      <c r="O26" s="101"/>
+      <c r="P26" s="80"/>
+    </row>
+    <row r="27" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="33" t="str">
         <f>_xlfn.XLOOKUP(B27,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11538,22 +11538,22 @@
       <c r="B27" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="112"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="117"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="112"/>
-      <c r="H27" s="112"/>
-      <c r="I27" s="112"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="120"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="101"/>
-      <c r="P27" s="101"/>
-    </row>
-    <row r="28" spans="1:16" ht="33" x14ac:dyDescent="0.5">
+      <c r="C27" s="93"/>
+      <c r="D27" s="85"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="96"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="85"/>
+      <c r="K27" s="85"/>
+      <c r="L27" s="85"/>
+      <c r="M27" s="106"/>
+      <c r="N27" s="106"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="81"/>
+    </row>
+    <row r="28" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A28" s="31" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11561,51 +11561,51 @@
       <c r="B28" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="110">
+      <c r="C28" s="91">
         <v>2</v>
       </c>
-      <c r="D28" s="113" t="s">
+      <c r="D28" s="94" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="116" t="s">
-        <v>643</v>
-      </c>
-      <c r="F28" s="114" t="s">
+      <c r="E28" s="97" t="s">
+        <v>642</v>
+      </c>
+      <c r="F28" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="113"/>
-      <c r="H28" s="113" t="s">
+      <c r="G28" s="94"/>
+      <c r="H28" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="I28" s="113">
+      <c r="I28" s="94">
         <v>2</v>
       </c>
-      <c r="J28" s="113">
+      <c r="J28" s="94">
         <f>12*I28</f>
         <v>24</v>
       </c>
-      <c r="K28" s="113">
+      <c r="K28" s="94">
         <f>36*I28</f>
         <v>72</v>
       </c>
-      <c r="L28" s="113">
+      <c r="L28" s="94">
         <f>SUM(J28:K33)</f>
         <v>96</v>
       </c>
-      <c r="M28" s="102" t="s">
-        <v>623</v>
-      </c>
-      <c r="N28" s="102" t="s">
+      <c r="M28" s="82" t="s">
+        <v>622</v>
+      </c>
+      <c r="N28" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O28" s="102" t="s">
+      <c r="O28" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="P28" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="P28" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A29" s="29" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11613,22 +11613,22 @@
       <c r="B29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="111"/>
-      <c r="D29" s="82"/>
-      <c r="E29" s="108"/>
-      <c r="F29" s="106"/>
-      <c r="G29" s="82"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="82"/>
-      <c r="J29" s="82"/>
-      <c r="K29" s="82"/>
-      <c r="L29" s="82"/>
-      <c r="M29" s="81"/>
-      <c r="N29" s="81"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="100"/>
-    </row>
-    <row r="30" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="C29" s="92"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="87"/>
+      <c r="G29" s="84"/>
+      <c r="H29" s="84"/>
+      <c r="I29" s="84"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="101"/>
+      <c r="N29" s="101"/>
+      <c r="O29" s="101"/>
+      <c r="P29" s="80"/>
+    </row>
+    <row r="30" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A30" s="29" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11636,22 +11636,22 @@
       <c r="B30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="111"/>
-      <c r="D30" s="82"/>
-      <c r="E30" s="108"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="82"/>
-      <c r="I30" s="82"/>
-      <c r="J30" s="82"/>
-      <c r="K30" s="82"/>
-      <c r="L30" s="82"/>
-      <c r="M30" s="81"/>
-      <c r="N30" s="81"/>
-      <c r="O30" s="81"/>
-      <c r="P30" s="100"/>
-    </row>
-    <row r="31" spans="1:16" ht="66" x14ac:dyDescent="0.5">
+      <c r="C30" s="92"/>
+      <c r="D30" s="84"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="84"/>
+      <c r="H30" s="84"/>
+      <c r="I30" s="84"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="101"/>
+      <c r="N30" s="101"/>
+      <c r="O30" s="101"/>
+      <c r="P30" s="80"/>
+    </row>
+    <row r="31" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A31" s="29" t="str">
         <f>_xlfn.XLOOKUP(B31,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11659,22 +11659,22 @@
       <c r="B31" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="111"/>
-      <c r="D31" s="82"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="82"/>
-      <c r="H31" s="82"/>
-      <c r="I31" s="82"/>
-      <c r="J31" s="82"/>
-      <c r="K31" s="82"/>
-      <c r="L31" s="82"/>
-      <c r="M31" s="81"/>
-      <c r="N31" s="81"/>
-      <c r="O31" s="81"/>
-      <c r="P31" s="100"/>
-    </row>
-    <row r="32" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="C31" s="92"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="84"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="84"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="101"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="80"/>
+    </row>
+    <row r="32" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A32" s="29" t="str">
         <f>_xlfn.XLOOKUP(B32,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11682,22 +11682,22 @@
       <c r="B32" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C32" s="111"/>
-      <c r="D32" s="82"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="106"/>
-      <c r="G32" s="82"/>
-      <c r="H32" s="82"/>
-      <c r="I32" s="82"/>
-      <c r="J32" s="82"/>
-      <c r="K32" s="82"/>
-      <c r="L32" s="82"/>
-      <c r="M32" s="81"/>
-      <c r="N32" s="81"/>
-      <c r="O32" s="81"/>
-      <c r="P32" s="100"/>
-    </row>
-    <row r="33" spans="1:16" ht="66.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C32" s="92"/>
+      <c r="D32" s="84"/>
+      <c r="E32" s="89"/>
+      <c r="F32" s="87"/>
+      <c r="G32" s="84"/>
+      <c r="H32" s="84"/>
+      <c r="I32" s="84"/>
+      <c r="J32" s="84"/>
+      <c r="K32" s="84"/>
+      <c r="L32" s="84"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="80"/>
+    </row>
+    <row r="33" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="33" t="str">
         <f>_xlfn.XLOOKUP(B33,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11705,22 +11705,22 @@
       <c r="B33" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="112"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="117"/>
-      <c r="F33" s="115"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="120"/>
-      <c r="N33" s="120"/>
-      <c r="O33" s="120"/>
-      <c r="P33" s="101"/>
-    </row>
-    <row r="34" spans="1:16" ht="82.5" x14ac:dyDescent="0.5">
+      <c r="C33" s="93"/>
+      <c r="D33" s="85"/>
+      <c r="E33" s="98"/>
+      <c r="F33" s="96"/>
+      <c r="G33" s="85"/>
+      <c r="H33" s="85"/>
+      <c r="I33" s="85"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="85"/>
+      <c r="L33" s="85"/>
+      <c r="M33" s="106"/>
+      <c r="N33" s="106"/>
+      <c r="O33" s="106"/>
+      <c r="P33" s="81"/>
+    </row>
+    <row r="34" spans="1:16" ht="90" x14ac:dyDescent="0.5">
       <c r="A34" s="31" t="str">
         <f>_xlfn.XLOOKUP(B34,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11728,74 +11728,74 @@
       <c r="B34" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="110">
+      <c r="C34" s="91">
         <v>2</v>
       </c>
-      <c r="D34" s="113" t="s">
+      <c r="D34" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="116" t="s">
-        <v>642</v>
-      </c>
-      <c r="F34" s="114" t="s">
+      <c r="E34" s="97" t="s">
+        <v>641</v>
+      </c>
+      <c r="F34" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="G34" s="113"/>
-      <c r="H34" s="113" t="s">
+      <c r="G34" s="94"/>
+      <c r="H34" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="I34" s="113">
+      <c r="I34" s="94">
         <v>3</v>
       </c>
-      <c r="J34" s="113">
+      <c r="J34" s="94">
         <f>12*I34</f>
         <v>36</v>
       </c>
-      <c r="K34" s="113">
+      <c r="K34" s="94">
         <f>36*I34</f>
         <v>108</v>
       </c>
-      <c r="L34" s="113">
+      <c r="L34" s="94">
         <f>SUM(J34:K37)</f>
         <v>144</v>
       </c>
-      <c r="M34" s="102" t="s">
-        <v>624</v>
-      </c>
-      <c r="N34" s="102" t="s">
+      <c r="M34" s="82" t="s">
+        <v>623</v>
+      </c>
+      <c r="N34" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O34" s="102" t="s">
+      <c r="O34" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="P34" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="66" x14ac:dyDescent="0.5">
+      <c r="P34" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="72" x14ac:dyDescent="0.5">
       <c r="A35" s="29" t="str">
         <f>_xlfn.XLOOKUP(B35,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="C35" s="111"/>
-      <c r="D35" s="82"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
-      <c r="I35" s="82"/>
-      <c r="J35" s="82"/>
-      <c r="K35" s="82"/>
-      <c r="L35" s="82"/>
-      <c r="M35" s="81"/>
-      <c r="N35" s="81"/>
-      <c r="O35" s="81"/>
-      <c r="P35" s="100"/>
-    </row>
-    <row r="36" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+        <v>635</v>
+      </c>
+      <c r="C35" s="92"/>
+      <c r="D35" s="84"/>
+      <c r="E35" s="89"/>
+      <c r="F35" s="87"/>
+      <c r="G35" s="84"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="84"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="101"/>
+      <c r="N35" s="101"/>
+      <c r="O35" s="101"/>
+      <c r="P35" s="80"/>
+    </row>
+    <row r="36" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A36" s="29" t="str">
         <f>_xlfn.XLOOKUP(B36,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11803,22 +11803,22 @@
       <c r="B36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="111"/>
-      <c r="D36" s="82"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="106"/>
-      <c r="G36" s="82"/>
-      <c r="H36" s="82"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="82"/>
-      <c r="K36" s="82"/>
-      <c r="L36" s="82"/>
-      <c r="M36" s="81"/>
-      <c r="N36" s="81"/>
-      <c r="O36" s="81"/>
-      <c r="P36" s="100"/>
-    </row>
-    <row r="37" spans="1:16" ht="66.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C36" s="92"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="89"/>
+      <c r="F36" s="87"/>
+      <c r="G36" s="84"/>
+      <c r="H36" s="84"/>
+      <c r="I36" s="84"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="84"/>
+      <c r="M36" s="101"/>
+      <c r="N36" s="101"/>
+      <c r="O36" s="101"/>
+      <c r="P36" s="80"/>
+    </row>
+    <row r="37" spans="1:16" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="33" t="str">
         <f>_xlfn.XLOOKUP(B37,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saber</v>
@@ -11826,22 +11826,22 @@
       <c r="B37" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="112"/>
-      <c r="D37" s="104"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="115"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="120"/>
-      <c r="N37" s="120"/>
-      <c r="O37" s="120"/>
-      <c r="P37" s="101"/>
-    </row>
-    <row r="38" spans="1:16" ht="49.5" x14ac:dyDescent="0.5">
+      <c r="C37" s="93"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="85"/>
+      <c r="H37" s="85"/>
+      <c r="I37" s="85"/>
+      <c r="J37" s="85"/>
+      <c r="K37" s="85"/>
+      <c r="L37" s="85"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="106"/>
+      <c r="O37" s="106"/>
+      <c r="P37" s="81"/>
+    </row>
+    <row r="38" spans="1:16" ht="54" x14ac:dyDescent="0.5">
       <c r="A38" s="31" t="str">
         <f>_xlfn.XLOOKUP(B38,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberser</v>
@@ -11849,51 +11849,51 @@
       <c r="B38" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="110">
+      <c r="C38" s="91">
         <v>2</v>
       </c>
-      <c r="D38" s="113" t="s">
+      <c r="D38" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="E38" s="116" t="s">
-        <v>641</v>
-      </c>
-      <c r="F38" s="114" t="s">
+      <c r="E38" s="97" t="s">
+        <v>640</v>
+      </c>
+      <c r="F38" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113" t="s">
+      <c r="G38" s="94"/>
+      <c r="H38" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="113">
+      <c r="I38" s="94">
         <v>3</v>
       </c>
-      <c r="J38" s="113">
+      <c r="J38" s="94">
         <f>12*I38</f>
         <v>36</v>
       </c>
-      <c r="K38" s="113">
+      <c r="K38" s="94">
         <f>36*I38</f>
         <v>108</v>
       </c>
-      <c r="L38" s="113">
+      <c r="L38" s="94">
         <f>SUM(J38:K40)</f>
         <v>144</v>
       </c>
-      <c r="M38" s="102" t="s">
-        <v>620</v>
-      </c>
-      <c r="N38" s="102" t="s">
+      <c r="M38" s="82" t="s">
+        <v>619</v>
+      </c>
+      <c r="N38" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="O38" s="102" t="s">
+      <c r="O38" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="P38" s="102" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="82.5" x14ac:dyDescent="0.5">
+      <c r="P38" s="82" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" ht="90" x14ac:dyDescent="0.5">
       <c r="A39" s="29" t="str">
         <f>_xlfn.XLOOKUP(B39,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11901,22 +11901,22 @@
       <c r="B39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="111"/>
-      <c r="D39" s="82"/>
-      <c r="E39" s="108"/>
-      <c r="F39" s="106"/>
-      <c r="G39" s="82"/>
-      <c r="H39" s="82"/>
-      <c r="I39" s="82"/>
-      <c r="J39" s="82"/>
-      <c r="K39" s="82"/>
-      <c r="L39" s="82"/>
-      <c r="M39" s="81"/>
-      <c r="N39" s="81"/>
-      <c r="O39" s="81"/>
-      <c r="P39" s="100"/>
-    </row>
-    <row r="40" spans="1:16" ht="50" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C39" s="92"/>
+      <c r="D39" s="84"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="87"/>
+      <c r="G39" s="84"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="84"/>
+      <c r="J39" s="84"/>
+      <c r="K39" s="84"/>
+      <c r="L39" s="84"/>
+      <c r="M39" s="101"/>
+      <c r="N39" s="101"/>
+      <c r="O39" s="101"/>
+      <c r="P39" s="80"/>
+    </row>
+    <row r="40" spans="1:16" ht="54.6" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="33" t="str">
         <f>_xlfn.XLOOKUP(B40,'Paso 3 Redacción RA '!I$3:I$11,'Paso 3 Redacción RA '!C$3:C$11,,0,1)</f>
         <v>Saberhacer</v>
@@ -11924,22 +11924,22 @@
       <c r="B40" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C40" s="111"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="115"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="120"/>
-      <c r="N40" s="120"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="101"/>
-    </row>
-    <row r="41" spans="1:16" ht="30" x14ac:dyDescent="0.5">
+      <c r="C40" s="92"/>
+      <c r="D40" s="85"/>
+      <c r="E40" s="98"/>
+      <c r="F40" s="96"/>
+      <c r="G40" s="85"/>
+      <c r="H40" s="85"/>
+      <c r="I40" s="85"/>
+      <c r="J40" s="85"/>
+      <c r="K40" s="85"/>
+      <c r="L40" s="85"/>
+      <c r="M40" s="106"/>
+      <c r="N40" s="106"/>
+      <c r="O40" s="106"/>
+      <c r="P40" s="81"/>
+    </row>
+    <row r="41" spans="1:16" ht="27.6" x14ac:dyDescent="0.5">
       <c r="B41" s="4"/>
       <c r="C41" s="62" t="s">
         <v>69</v>
@@ -11958,25 +11958,27 @@
       </c>
       <c r="M41" s="5"/>
     </row>
-    <row r="42" spans="1:16" ht="45" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:16" ht="41.4" x14ac:dyDescent="0.5">
       <c r="C42" s="36"/>
       <c r="F42" s="7"/>
       <c r="H42" s="65" t="s">
         <v>71</v>
       </c>
       <c r="I42" s="66">
-        <v>5</v>
+        <f>SUMIFS(I3:I40,G3:G40,"X")</f>
+        <v>15</v>
       </c>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:16" ht="45" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:16" ht="41.4" x14ac:dyDescent="0.5">
       <c r="C43" s="36"/>
       <c r="F43" s="7"/>
       <c r="H43" s="65" t="s">
         <v>72</v>
       </c>
       <c r="I43" s="66">
-        <v>4</v>
+        <f>SUMIFS(I3:I40,H3:H40,"X")</f>
+        <v>10</v>
       </c>
       <c r="M43" s="5"/>
     </row>
@@ -12134,13 +12136,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E64FCBD-ADC1-40F4-BFE8-98BA12AA9611}">
   <dimension ref="B1:D37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
-    <col min="4" max="4" width="99.36328125" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
+    <col min="4" max="4" width="99.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="30.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:4" ht="31.2" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>73</v>
       </c>
@@ -12148,182 +12150,182 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:4" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="37" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="37" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B37" s="1" t="s">
         <v>107</v>
       </c>
@@ -12339,48 +12341,48 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A97597-49CE-4804-805A-84A20592BE98}">
   <dimension ref="A1:BK108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.453125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.36328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.36328125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.6328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.453125" style="1" customWidth="1"/>
-    <col min="19" max="33" width="17.453125" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.453125" style="1" customWidth="1"/>
-    <col min="38" max="38" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="26.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="20.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="21.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.6328125" style="1" customWidth="1"/>
-    <col min="45" max="45" width="26.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="21.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="24.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="23.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="22.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="32.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="13.36328125" style="1" customWidth="1"/>
-    <col min="54" max="54" width="23.81640625" style="1" customWidth="1"/>
-    <col min="55" max="55" width="22.453125" style="1" customWidth="1"/>
-    <col min="56" max="56" width="24.1796875" style="1" customWidth="1"/>
-    <col min="57" max="57" width="27.81640625" style="1" customWidth="1"/>
-    <col min="58" max="58" width="24.6328125" style="1" customWidth="1"/>
-    <col min="59" max="59" width="22.6328125" style="1" customWidth="1"/>
-    <col min="60" max="63" width="13.36328125" style="1" customWidth="1"/>
-    <col min="64" max="16384" width="11.453125" style="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.6640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.44140625" style="1" customWidth="1"/>
+    <col min="19" max="33" width="17.44140625" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.44140625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="23.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="21.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.6640625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="19.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="23.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="32.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="13.33203125" style="1" customWidth="1"/>
+    <col min="54" max="54" width="23.77734375" style="1" customWidth="1"/>
+    <col min="55" max="55" width="22.44140625" style="1" customWidth="1"/>
+    <col min="56" max="56" width="24.21875" style="1" customWidth="1"/>
+    <col min="57" max="57" width="27.77734375" style="1" customWidth="1"/>
+    <col min="58" max="58" width="24.6640625" style="1" customWidth="1"/>
+    <col min="59" max="59" width="22.6640625" style="1" customWidth="1"/>
+    <col min="60" max="63" width="13.33203125" style="1" customWidth="1"/>
+    <col min="64" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:63" x14ac:dyDescent="0.5">
